--- a/artfynd/A 10745-2026 artfynd.xlsx
+++ b/artfynd/A 10745-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376305</v>
       </c>
       <c r="B2" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376310</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10745-2026 artfynd.xlsx
+++ b/artfynd/A 10745-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376305</v>
       </c>
       <c r="B2" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376310</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10745-2026 artfynd.xlsx
+++ b/artfynd/A 10745-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376305</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376310</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10745-2026 artfynd.xlsx
+++ b/artfynd/A 10745-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376305</v>
       </c>
       <c r="B2" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376310</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10745-2026 artfynd.xlsx
+++ b/artfynd/A 10745-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376305</v>
       </c>
       <c r="B2" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376310</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
